--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/DISTRICT_OF_COLUMBIA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/DISTRICT_OF_COLUMBIA_2015.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C117">
